--- a/data/trans_orig/IP07A11-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07A11-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido estar al aire libre en 2007 (tasa de respuesta: 99,6%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre, percibida por el adulto en 2007 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10247</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21227</t>
+          <t>21515</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18330</t>
+          <t>18103</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31882</t>
+          <t>32046</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31997</t>
+          <t>32601</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49118</t>
+          <t>49123</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,92%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33078</t>
+          <t>32421</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45773</t>
+          <t>45433</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42226</t>
+          <t>41885</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55907</t>
+          <t>56453</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>79979</t>
+          <t>78824</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98194</t>
+          <t>97248</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>67,15%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4856</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13936</t>
+          <t>13862</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3337</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11404</t>
+          <t>11402</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9841</t>
+          <t>10370</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22651</t>
+          <t>22263</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>3539</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27430</t>
+          <t>27591</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42617</t>
+          <t>42393</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32519</t>
+          <t>33197</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47914</t>
+          <t>47831</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63992</t>
+          <t>65405</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86031</t>
+          <t>86581</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,6%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46405</t>
+          <t>46184</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>62093</t>
+          <t>62408</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34268</t>
+          <t>34335</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50193</t>
+          <t>49563</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85456</t>
+          <t>84768</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>106907</t>
+          <t>107825</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>53,06%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9427</t>
+          <t>9194</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20543</t>
+          <t>20474</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9846</t>
+          <t>10533</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21035</t>
+          <t>21263</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21710</t>
+          <t>22136</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>37922</t>
+          <t>37724</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,56%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3258</t>
+          <t>3686</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4647</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3769</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4064</t>
+          <t>4566</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20546</t>
+          <t>20329</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32107</t>
+          <t>32258</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24682</t>
+          <t>25275</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37736</t>
+          <t>38054</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>48775</t>
+          <t>48581</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>66598</t>
+          <t>66313</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,07%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18068</t>
+          <t>17381</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29268</t>
+          <t>29406</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22077</t>
+          <t>21986</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35326</t>
+          <t>34440</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43103</t>
+          <t>42517</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60324</t>
+          <t>59840</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>46,99%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6304</t>
+          <t>6747</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15055</t>
+          <t>15650</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2768</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10640</t>
+          <t>10391</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11367</t>
+          <t>11355</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>22713</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>4610</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>4164</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>481</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2224</t>
+          <t>2374</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2484</t>
+          <t>2219</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25196</t>
+          <t>25284</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41184</t>
+          <t>41780</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33941</t>
+          <t>33329</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49660</t>
+          <t>49936</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63264</t>
+          <t>64043</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>86802</t>
+          <t>86197</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,09%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>31378</t>
+          <t>30858</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>47754</t>
+          <t>47896</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>32476</t>
+          <t>32423</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47760</t>
+          <t>47867</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>69005</t>
+          <t>67834</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>91018</t>
+          <t>89330</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>46,73%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12087</t>
+          <t>11875</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24486</t>
+          <t>24953</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10812</t>
+          <t>10565</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22957</t>
+          <t>22515</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>25455</t>
+          <t>25341</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>43294</t>
+          <t>42648</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>705</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5957</t>
+          <t>6470</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1407</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7762</t>
+          <t>8342</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>95083</t>
+          <t>96092</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>122243</t>
+          <t>124437</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>123782</t>
+          <t>125182</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>153070</t>
+          <t>154451</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>228089</t>
+          <t>226530</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>267934</t>
+          <t>268509</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,28%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>141799</t>
+          <t>141077</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>170559</t>
+          <t>170483</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>145222</t>
+          <t>144566</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>173807</t>
+          <t>173229</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>293619</t>
+          <t>296817</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>335958</t>
+          <t>339033</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,86%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>41181</t>
+          <t>40593</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>62311</t>
+          <t>62198</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>33877</t>
+          <t>34187</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>53772</t>
+          <t>54347</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>81324</t>
+          <t>79959</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>109493</t>
+          <t>108915</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8482</t>
+          <t>8497</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7125</t>
+          <t>7321</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>3874</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>12994</t>
+          <t>12982</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>4296</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido estar al aire libre en 2012 (tasa de respuesta: 98,23%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre, percibida por el adulto en 2012 (tasa de respuesta: 98,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33907</t>
+          <t>34805</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47249</t>
+          <t>46813</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37863</t>
+          <t>37949</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52290</t>
+          <t>51549</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77538</t>
+          <t>76768</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95594</t>
+          <t>94748</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>68,51%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15533</t>
+          <t>16247</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28507</t>
+          <t>28672</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16187</t>
+          <t>16642</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30050</t>
+          <t>29737</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35648</t>
+          <t>36452</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53398</t>
+          <t>54680</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>39,54%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>664</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6760</t>
+          <t>6065</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7247</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>3229</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10686</t>
+          <t>10759</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t>4123</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3343</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3462</t>
+          <t>3486</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47168</t>
+          <t>47091</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63603</t>
+          <t>63145</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44209</t>
+          <t>42742</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59675</t>
+          <t>58903</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>96260</t>
+          <t>95433</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117634</t>
+          <t>117537</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>59,86%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28922</t>
+          <t>29833</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44233</t>
+          <t>44993</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31485</t>
+          <t>31651</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47087</t>
+          <t>47224</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>65535</t>
+          <t>65790</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>85888</t>
+          <t>88528</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>45,08%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10396</t>
+          <t>10634</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2599</t>
+          <t>2541</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10993</t>
+          <t>11281</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6782</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17680</t>
+          <t>17084</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>4513</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3285</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5698</t>
+          <t>5688</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28120</t>
+          <t>27888</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41447</t>
+          <t>40928</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34016</t>
+          <t>34375</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47082</t>
+          <t>46692</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>66199</t>
+          <t>66153</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84250</t>
+          <t>85048</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>62,51%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18393</t>
+          <t>18605</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31568</t>
+          <t>31047</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14522</t>
+          <t>14471</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26382</t>
+          <t>26325</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36591</t>
+          <t>36907</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>53320</t>
+          <t>54792</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>40,27%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3766</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12432</t>
+          <t>11639</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3639</t>
+          <t>4198</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12137</t>
+          <t>11716</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9278</t>
+          <t>9302</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20214</t>
+          <t>20026</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,72%</t>
         </is>
       </c>
     </row>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>4168</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3074</t>
+          <t>3495</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33424</t>
+          <t>32899</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49981</t>
+          <t>49542</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34130</t>
+          <t>35143</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51016</t>
+          <t>51240</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>73417</t>
+          <t>73175</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>95789</t>
+          <t>96712</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>52,43%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>31506</t>
+          <t>32010</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>47821</t>
+          <t>47819</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>33763</t>
+          <t>34428</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>50082</t>
+          <t>51098</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>69414</t>
+          <t>70284</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>92543</t>
+          <t>93395</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,63%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15612</t>
+          <t>15545</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2918</t>
+          <t>2858</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12089</t>
+          <t>11266</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10257</t>
+          <t>9408</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>24106</t>
+          <t>23297</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,63%</t>
         </is>
       </c>
     </row>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4313</t>
+          <t>4019</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>762</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>7203</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>158844</t>
+          <t>157065</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>187235</t>
+          <t>186000</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>166008</t>
+          <t>165792</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>195146</t>
+          <t>194485</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>332317</t>
+          <t>333438</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>373725</t>
+          <t>374374</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,14%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>107480</t>
+          <t>109631</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>137045</t>
+          <t>137987</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>109603</t>
+          <t>110293</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>138011</t>
+          <t>139073</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>225573</t>
+          <t>226943</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>265749</t>
+          <t>266584</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,69%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17927</t>
+          <t>18132</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>34330</t>
+          <t>33911</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>15609</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>30848</t>
+          <t>30594</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>37671</t>
+          <t>36600</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>59562</t>
+          <t>58208</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>626</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5727</t>
+          <t>5823</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8703</t>
+          <t>8633</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>11905</t>
+          <t>11374</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4513</t>
+          <t>4674</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>4194</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido estar al aire libre en 2016 (tasa de respuesta: 98,92%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre, percibida por el adulto en 2016 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31373</t>
+          <t>31659</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45467</t>
+          <t>45539</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33052</t>
+          <t>32216</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47670</t>
+          <t>47726</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68525</t>
+          <t>69412</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89894</t>
+          <t>89335</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>61,84%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15903</t>
+          <t>16045</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29801</t>
+          <t>29405</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>22064</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36817</t>
+          <t>37030</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41459</t>
+          <t>41752</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>61249</t>
+          <t>61029</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,24%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5818</t>
+          <t>5532</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15902</t>
+          <t>15864</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1553</t>
+          <t>1570</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8994</t>
+          <t>9456</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8758</t>
+          <t>8742</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21500</t>
+          <t>22256</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,41%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45178</t>
+          <t>45165</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61922</t>
+          <t>61725</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44760</t>
+          <t>45242</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61690</t>
+          <t>62084</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>96246</t>
+          <t>93770</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>118665</t>
+          <t>118014</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>55,23%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34245</t>
+          <t>33859</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49457</t>
+          <t>49672</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34968</t>
+          <t>35578</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51914</t>
+          <t>52195</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>74197</t>
+          <t>74411</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>96271</t>
+          <t>97086</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,44%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4258</t>
+          <t>3784</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12474</t>
+          <t>12481</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>2693</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10699</t>
+          <t>10644</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8439</t>
+          <t>8986</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19505</t>
+          <t>21014</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>635</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7265</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8557</t>
+          <t>7931</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11681</t>
+          <t>11744</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>2766</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3444</t>
+          <t>3466</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4476</t>
+          <t>4608</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32238</t>
+          <t>31741</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45275</t>
+          <t>45439</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36727</t>
+          <t>36051</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50304</t>
+          <t>50589</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71852</t>
+          <t>72029</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>91802</t>
+          <t>91637</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,23%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16588</t>
+          <t>17157</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29038</t>
+          <t>29663</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21897</t>
+          <t>21409</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34975</t>
+          <t>35352</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41077</t>
+          <t>40504</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60359</t>
+          <t>59838</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>39,98%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6403</t>
+          <t>6716</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16138</t>
+          <t>16352</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2569</t>
+          <t>2450</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10829</t>
+          <t>10324</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10910</t>
+          <t>10398</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23202</t>
+          <t>22625</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -9872,7 +9872,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3168</t>
+          <t>3384</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34800</t>
+          <t>35184</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53246</t>
+          <t>52361</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41702</t>
+          <t>42018</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>58494</t>
+          <t>58214</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>81147</t>
+          <t>81479</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>105889</t>
+          <t>106143</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,61%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>32706</t>
+          <t>32446</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>50727</t>
+          <t>49476</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>29111</t>
+          <t>28658</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>45533</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>66334</t>
+          <t>65873</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>88483</t>
+          <t>89943</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>42,88%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11741</t>
+          <t>11973</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24612</t>
+          <t>25743</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9718</t>
+          <t>9623</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>21566</t>
+          <t>21143</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>24478</t>
+          <t>24665</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>42544</t>
+          <t>42279</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,16%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7804</t>
+          <t>7758</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3272</t>
+          <t>3172</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1417</t>
+          <t>1554</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9377</t>
+          <t>9010</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5324</t>
+          <t>5923</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10589,7 +10589,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4877</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>158193</t>
+          <t>160545</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>189781</t>
+          <t>190763</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>170950</t>
+          <t>173250</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>204750</t>
+          <t>202594</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>341192</t>
+          <t>340281</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>382552</t>
+          <t>384763</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>53,62%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>112452</t>
+          <t>113727</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>142691</t>
+          <t>143683</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>122087</t>
+          <t>122059</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>152413</t>
+          <t>151755</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,47 +10907,47 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
+          <t>33,78%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>42,0%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>264724</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>242439</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>285390</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>36,89%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>33,79%</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>42,18%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>264724</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>243973</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>285832</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>36,89%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>34,0%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,77%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>36812</t>
+          <t>36606</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>56644</t>
+          <t>57601</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>23467</t>
+          <t>21977</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>40467</t>
+          <t>39776</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>63395</t>
+          <t>62416</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>90630</t>
+          <t>91134</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>12156</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>8908</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5869</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>16343</t>
+          <t>17096</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -11201,7 +11201,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5466</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11236,7 +11236,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>692</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7634</t>
+          <t>7901</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
